--- a/sampleprojects/CorporateTax/excel/states/AZ_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/AZ_corp.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>DT: Determine AZ Filing Requirement</t>
   </si>
@@ -145,7 +145,7 @@
     <t>Calculate tax at 4.9% flat rate; // Arizona uses 4.9% flat rate; set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits; set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
-    <t>if apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits &gt; 0.0 then set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits; else set apportionment.state_tax = 0.0; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>if apportionment.state_taxable_income * az_apportionment.state_tax_rate - apportionment.state_credits &gt; 0.0 then set apportionment.state_tax = apportionment.state_taxable_income * az_apportionment.state_tax_rate - apportionment.state_credits; else set apportionment.state_tax = 0.0; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No nexus - no tax liability; // No Arizona nexus - no tax liability; set apportionment.state_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
@@ -196,10 +196,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>az_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -227,36 +227,6 @@
   </si>
   <si>
     <t>AZ economic nexus gross receipts threshold: $100,000 (AZ Rev. Stat. § 43-1102)</t>
-  </si>
-  <si>
-    <t>state_additions</t>
-  </si>
-  <si>
-    <t>0.0</t>
-  </si>
-  <si>
-    <t>AZ additions: federal interest, IRC 199A addback, bonus depreciation (if decoupled)</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>AZ</t>
-  </si>
-  <si>
-    <t>Arizona two-letter state code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>AZ tax credits: R&amp;D, renewable energy, employment, film production</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>AZ subtractions: AZ municipal interest, state taxes, AZ NOL</t>
   </si>
   <si>
     <t>state_tax_rate</t>
@@ -2545,14 +2515,14 @@
       <c r="B7" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>62</v>
+      <c r="C7" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -2561,7 +2531,7 @@
         <v>64</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -2576,170 +2546,6 @@
         <v>14</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
         <v>14</v>
       </c>
     </row>
